--- a/resources/County Codes.xlsx
+++ b/resources/County Codes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tkdma\Documents\Projects\Draw and Schedule\input files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\Programming Projects\Python\Ranking_and_Draw\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3F1A0D-EA65-4298-91D5-B96DFE80695D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98BE635-5530-4947-888D-2E03FC4C2628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="1356" windowWidth="17280" windowHeight="8880" xr2:uid="{52FAFDFA-62B8-4F33-BA33-EE628FAA76B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{52FAFDFA-62B8-4F33-BA33-EE628FAA76B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="145">
   <si>
     <t>Essex</t>
   </si>
@@ -452,6 +452,21 @@
   </si>
   <si>
     <t>Leicester</t>
+  </si>
+  <si>
+    <t>West Yorkshire</t>
+  </si>
+  <si>
+    <t>Wales</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Do</t>
   </si>
 </sst>
 </file>
@@ -806,13 +821,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B77065-09BA-43F0-B499-09A8567FCEEA}">
-  <dimension ref="A1:B74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B146"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="1" max="1" width="26.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -820,7 +835,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -828,7 +843,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -836,7 +851,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -844,7 +859,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>62</v>
       </c>
@@ -852,7 +867,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -860,7 +875,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -868,7 +883,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -876,7 +891,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -884,7 +899,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -892,7 +907,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -900,22 +915,22 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -923,7 +938,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -931,7 +946,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -939,17 +954,20 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -957,7 +975,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -965,7 +983,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -973,7 +991,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -981,7 +999,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -989,7 +1007,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -997,7 +1015,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1005,7 +1023,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -1013,7 +1031,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1021,7 +1039,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1029,7 +1047,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1037,7 +1055,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1045,7 +1063,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -1053,7 +1071,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -1061,7 +1079,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -1069,7 +1087,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -1077,7 +1095,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -1085,7 +1103,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -1093,7 +1111,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -1101,7 +1119,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1109,7 +1127,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>24</v>
       </c>
@@ -1117,7 +1135,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1125,7 +1143,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>21</v>
       </c>
@@ -1133,7 +1151,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>58</v>
       </c>
@@ -1141,7 +1159,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -1149,12 +1167,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -1162,7 +1180,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -1170,7 +1188,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -1178,7 +1196,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>30</v>
       </c>
@@ -1186,7 +1204,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -1194,7 +1212,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>45</v>
       </c>
@@ -1202,7 +1220,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -1210,7 +1228,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>38</v>
       </c>
@@ -1218,7 +1236,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>64</v>
       </c>
@@ -1226,7 +1244,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1234,7 +1252,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -1242,7 +1260,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -1250,7 +1268,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -1258,7 +1276,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -1266,7 +1284,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -1274,7 +1292,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1300,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>36</v>
       </c>
@@ -1290,7 +1308,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>10</v>
       </c>
@@ -1298,7 +1316,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -1306,7 +1324,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -1314,7 +1332,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -1322,7 +1340,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>32</v>
       </c>
@@ -1330,7 +1348,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>41</v>
       </c>
@@ -1338,7 +1356,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>33</v>
       </c>
@@ -1346,7 +1364,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -1354,7 +1372,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>129</v>
       </c>
@@ -1362,7 +1380,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>136</v>
       </c>
@@ -1370,7 +1388,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>138</v>
       </c>
@@ -1378,12 +1396,588 @@
         <v>91</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>139</v>
       </c>
       <c r="B74" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>142</v>
+      </c>
+      <c r="B77" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>70</v>
+      </c>
+      <c r="B79" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>114</v>
+      </c>
+      <c r="B81" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>87</v>
+      </c>
+      <c r="B82" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>71</v>
+      </c>
+      <c r="B83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>72</v>
+      </c>
+      <c r="B84" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>73</v>
+      </c>
+      <c r="B85" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>81</v>
+      </c>
+      <c r="B86" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>137</v>
+      </c>
+      <c r="B91" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>80</v>
+      </c>
+      <c r="B92" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>83</v>
+      </c>
+      <c r="B93" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>97</v>
+      </c>
+      <c r="B95" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>107</v>
+      </c>
+      <c r="B97" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>116</v>
+      </c>
+      <c r="B98" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>127</v>
+      </c>
+      <c r="B99" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>126</v>
+      </c>
+      <c r="B100" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>74</v>
+      </c>
+      <c r="B101" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>82</v>
+      </c>
+      <c r="B103" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>117</v>
+      </c>
+      <c r="B104" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>100</v>
+      </c>
+      <c r="B105" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>118</v>
+      </c>
+      <c r="B108" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>85</v>
+      </c>
+      <c r="B109" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>95</v>
+      </c>
+      <c r="B110" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>109</v>
+      </c>
+      <c r="B112" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>78</v>
+      </c>
+      <c r="B113" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>84</v>
+      </c>
+      <c r="B115" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>77</v>
+      </c>
+      <c r="B117" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>99</v>
+      </c>
+      <c r="B118" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>106</v>
+      </c>
+      <c r="B119" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>92</v>
+      </c>
+      <c r="B120" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>131</v>
+      </c>
+      <c r="B121" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>91</v>
+      </c>
+      <c r="B122" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>93</v>
+      </c>
+      <c r="B123" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>76</v>
+      </c>
+      <c r="B126" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>103</v>
+      </c>
+      <c r="B127" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>105</v>
+      </c>
+      <c r="B128" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>75</v>
+      </c>
+      <c r="B130" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>121</v>
+      </c>
+      <c r="B131" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>104</v>
+      </c>
+      <c r="B132" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>96</v>
+      </c>
+      <c r="B133" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>90</v>
+      </c>
+      <c r="B134" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>122</v>
+      </c>
+      <c r="B135" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>94</v>
+      </c>
+      <c r="B136" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>69</v>
+      </c>
+      <c r="B137" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>125</v>
+      </c>
+      <c r="B138" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>124</v>
+      </c>
+      <c r="B139" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>89</v>
+      </c>
+      <c r="B140" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>130</v>
+      </c>
+      <c r="B141" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>133</v>
+      </c>
+      <c r="B142" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>91</v>
+      </c>
+      <c r="B143" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>110</v>
+      </c>
+      <c r="B144" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>89</v>
+      </c>
+      <c r="B145" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>69</v>
+      </c>
+      <c r="B146" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
